--- a/api/templates/export/devices/es.xlsx
+++ b/api/templates/export/devices/es.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="21126"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-20.04\home\ubuntu\aspect\api\templates\export\devices\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect-node-12\api\templates\export\devices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A7D1B7B-43F0-4C60-8EE9-71E899767973}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="480" windowWidth="20734" windowHeight="11760" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="480" windowWidth="20736" windowHeight="11760" tabRatio="815"/>
   </bookViews>
   <sheets>
     <sheet name="Devices" sheetId="1" r:id="rId1"/>
@@ -172,12 +171,6 @@
     <t>Estado</t>
   </si>
   <si>
-    <t>Disponibilidad</t>
-  </si>
-  <si>
-    <t>Tasa de error</t>
-  </si>
-  <si>
     <t>Problemas</t>
   </si>
   <si>
@@ -194,12 +187,18 @@
   </si>
   <si>
     <t># Este mes</t>
+  </si>
+  <si>
+    <t>% Fallos de prueba</t>
+  </si>
+  <si>
+    <t>% Activo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
   </numFmts>
@@ -502,7 +501,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4">
-    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -839,44 +838,44 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J8"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.9" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.5" style="9" customWidth="1"/>
-    <col min="2" max="2" width="23.140625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" style="15" customWidth="1"/>
+    <col min="2" max="2" width="23.09765625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="13.69921875" style="15" customWidth="1"/>
     <col min="4" max="4" width="11.5" style="15" customWidth="1"/>
-    <col min="5" max="5" width="28.640625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="28.59765625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" style="3" customWidth="1"/>
     <col min="7" max="7" width="20" style="3" customWidth="1"/>
-    <col min="8" max="8" width="18.7109375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="18.69921875" style="3" customWidth="1"/>
     <col min="9" max="9" width="18" style="3" customWidth="1"/>
-    <col min="10" max="10" width="16.35546875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="16.3984375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="20.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="10" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>45</v>
       </c>
       <c r="C2" s="15"/>
       <c r="D2" s="15"/>
     </row>
-    <row r="3" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C3" s="15"/>
       <c r="D3" s="15"/>
     </row>
-    <row r="4" spans="1:10" ht="16.3" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>46</v>
       </c>
@@ -884,31 +883,31 @@
         <v>47</v>
       </c>
       <c r="C5" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="F5" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="H5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
         <v>33</v>
       </c>
@@ -940,7 +939,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C8" s="17"/>
       <c r="D8" s="17"/>
       <c r="E8" s="8"/>
@@ -957,16 +956,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultColWidth="8.640625" defaultRowHeight="22" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="22.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.2109375" customWidth="1"/>
-    <col min="3" max="3" width="100.640625" customWidth="1"/>
+    <col min="1" max="1" width="5.09765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.19921875" customWidth="1"/>
+    <col min="3" max="3" width="100.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -977,7 +976,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1001</v>
       </c>
@@ -988,7 +987,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>1002</v>
       </c>
@@ -999,7 +998,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>1004</v>
       </c>
@@ -1010,7 +1009,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>1005</v>
       </c>
@@ -1021,7 +1020,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>1006</v>
       </c>
@@ -1032,7 +1031,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>1007</v>
       </c>
@@ -1043,7 +1042,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>1017</v>
       </c>
@@ -1054,7 +1053,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>1018</v>
       </c>
@@ -1065,7 +1064,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>2003</v>
       </c>
@@ -1076,7 +1075,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>2005</v>
       </c>
@@ -1087,7 +1086,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>2008</v>
       </c>
@@ -1098,7 +1097,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>2009</v>
       </c>
@@ -1109,7 +1108,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>2011</v>
       </c>
@@ -1120,7 +1119,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>2014</v>
       </c>
@@ -1131,7 +1130,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>2016</v>
       </c>
@@ -1142,7 +1141,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>2018</v>
       </c>
@@ -1153,7 +1152,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>2022</v>
       </c>
@@ -1164,7 +1163,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>2025</v>
       </c>
@@ -1175,7 +1174,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>2032</v>
       </c>
@@ -1186,7 +1185,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>2034</v>
       </c>
@@ -1197,7 +1196,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>2037</v>
       </c>
@@ -1208,7 +1207,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>4010</v>
       </c>
@@ -1219,7 +1218,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
         <v>4017</v>
       </c>
@@ -1230,7 +1229,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>5006</v>
       </c>
@@ -1241,7 +1240,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>5007</v>
       </c>
@@ -1252,7 +1251,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>5011</v>
       </c>

--- a/api/templates/export/devices/es.xlsx
+++ b/api/templates/export/devices/es.xlsx
@@ -5,7 +5,7 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect-node-12\api\templates\export\devices\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect\api\templates\export\devices\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -180,19 +180,19 @@
     <t>Nombre corto</t>
   </si>
   <si>
-    <t># Último mes</t>
-  </si>
-  <si>
     <t>Última vez visto</t>
   </si>
   <si>
-    <t># Este mes</t>
-  </si>
-  <si>
-    <t>% Fallos de prueba</t>
-  </si>
-  <si>
-    <t>% Activo</t>
+    <t>Activo</t>
+  </si>
+  <si>
+    <t>Fallos de prueba</t>
+  </si>
+  <si>
+    <t>Último mes</t>
+  </si>
+  <si>
+    <t>Este mes</t>
   </si>
 </sst>
 </file>
@@ -883,10 +883,10 @@
         <v>47</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>48</v>
@@ -898,13 +898,13 @@
         <v>50</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
